--- a/data/trans_bre/P1410-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1410-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,94</t>
+          <t>-1,86</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-21,16%</t>
+          <t>-37,7%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,41; -0,51</t>
+          <t>-6,44; -0,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 4,21</t>
+          <t>-2,15; 4,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 4,26</t>
+          <t>-2,11; 4,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 1,93</t>
+          <t>-4,54; 0,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-92,26; 3,46</t>
+          <t>-92,29; 14,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-52,58; 223,94</t>
+          <t>-47,03; 280,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-58,25; 249,89</t>
+          <t>-55,03; 236,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-61,36; 69,22</t>
+          <t>-69,15; 11,72</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,18</t>
+          <t>-1,09</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-21,58%</t>
+          <t>-20,16%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 2,46</t>
+          <t>-3,34; 2,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 3,7</t>
+          <t>-1,72; 3,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 3,31</t>
+          <t>-1,99; 3,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 1,33</t>
+          <t>-3,79; 1,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,3; 52,75</t>
+          <t>-45,08; 55,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,75; 171,36</t>
+          <t>-37,79; 184,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,06; 119,35</t>
+          <t>-37,11; 115,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,88; 36,74</t>
+          <t>-53,56; 28,06</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 2,4</t>
+          <t>-3,61; 2,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 4,39</t>
+          <t>-2,76; 4,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 0,4</t>
+          <t>-5,76; 0,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 3,17</t>
+          <t>-2,62; 3,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-58,24; 96,15</t>
+          <t>-62,53; 99,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-41,89; 130,51</t>
+          <t>-43,1; 140,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-82,7; 15,93</t>
+          <t>-83,69; 20,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-36,9; 68,54</t>
+          <t>-35,16; 72,18</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,52</t>
+          <t>-1,51</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-42,16%</t>
+          <t>-26,74%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 1,5</t>
+          <t>-3,07; 1,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 2,4</t>
+          <t>-4,72; 1,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 9,58</t>
+          <t>1,74; 9,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 0,5</t>
+          <t>-4,43; 1,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,12; 96,16</t>
+          <t>-73,68; 74,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,52; 59,6</t>
+          <t>-58,35; 49,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,9; 381,27</t>
+          <t>27,86; 354,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,19; 11,55</t>
+          <t>-57,99; 44,5</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-2,36%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 2,85</t>
+          <t>-5,63; 2,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 5,89</t>
+          <t>-1,46; 6,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 2,49</t>
+          <t>-2,89; 2,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 2,48</t>
+          <t>-2,48; 2,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-73,75; 112,14</t>
+          <t>-78,91; 95,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-46,39; 346,48</t>
+          <t>-44,44; 412,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-87,03; 328,24</t>
+          <t>-100,0; 305,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-55,32; 120,76</t>
+          <t>-53,5; 136,21</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1,28</t>
+          <t>-1,18</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-16,51%</t>
+          <t>-15,5%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,35; -0,18</t>
+          <t>-6,22; -0,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 6,15</t>
+          <t>-2,33; 5,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 6,83</t>
+          <t>0,01; 7,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 2,06</t>
+          <t>-4,78; 1,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-87,67; 11,65</t>
+          <t>-89,49; 15,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-28,53; 203,02</t>
+          <t>-37,28; 185,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 622,26</t>
+          <t>-20,7; 551,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-44,2; 35,8</t>
+          <t>-48,77; 30,92</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-2,7</t>
+          <t>-1,15</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-41,29%</t>
+          <t>-17,6%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 2,89</t>
+          <t>-1,38; 3,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 0,31</t>
+          <t>-4,11; 0,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,96</t>
+          <t>-1,79; 2,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 0,06</t>
+          <t>-3,68; 1,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-32,06; 129,75</t>
+          <t>-32,56; 125,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-68,82; 10,2</t>
+          <t>-68,82; 12,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-36,18; 132,28</t>
+          <t>-41,7; 114,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-73,97; 0,62</t>
+          <t>-45,28; 21,94</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>-1,19</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-7,74%</t>
+          <t>-29,53%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 1,34</t>
+          <t>-2,62; 1,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,6</t>
+          <t>-0,87; 2,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 1,58</t>
+          <t>-2,55; 1,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,81</t>
+          <t>-2,63; 0,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-49,1; 35,82</t>
+          <t>-45,21; 41,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-26,14; 158,21</t>
+          <t>-30,02; 166,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-45,81; 46,71</t>
+          <t>-46,68; 51,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,42; 97,61</t>
+          <t>-54,21; 11,65</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1,08</t>
+          <t>-1,04</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-21,13%</t>
+          <t>-19,21%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 0,25</t>
+          <t>-1,77; 0,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,26</t>
+          <t>-0,7; 1,28</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,85</t>
+          <t>-0,26; 1,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,28</t>
+          <t>-2,02; -0,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-36,45; 6,14</t>
+          <t>-35,35; 3,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 39,18</t>
+          <t>-16,87; 36,96</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 55,83</t>
+          <t>-6,03; 53,74</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-36,57; 4,99</t>
+          <t>-33,81; -3,76</t>
         </is>
       </c>
     </row>
